--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487603_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487603_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.2474</v>
+        <v>10.3447</v>
       </c>
       <c r="E2" t="n">
-        <v>8.425800000000001</v>
+        <v>8.6866</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8216</v>
+        <v>1.6581</v>
       </c>
       <c r="G2" t="n">
         <v>6.2174</v>
@@ -610,13 +610,13 @@
         <v>1.9403</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0182</v>
+        <v>1.1154</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4621</v>
+        <v>0.7228</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5561</v>
+        <v>0.3926</v>
       </c>
       <c r="V2" t="n">
         <v>3.0119</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. ROSSI</t>
+          <t>O. MENDEZ BLANCO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0317</v>
+        <v>2.7463</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8099</v>
+        <v>3.3078</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7782</v>
+        <v>-0.5615</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.6348</v>
+        <v>0.9314</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1697</v>
+        <v>0.8791</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.8046</v>
+        <v>0.0523</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2638</v>
+        <v>1.9281</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3677</v>
+        <v>1.3141</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.1038</v>
+        <v>0.614</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8987</v>
+        <v>-0.9967</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1979</v>
+        <v>-0.435</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7008</v>
+        <v>-0.5617</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1642</v>
+        <v>-0.194</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9403</v>
+        <v>1.3582</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5605</v>
+        <v>-0.291</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8162</v>
+        <v>0.0678</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2557</v>
+        <v>-0.3589</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3299</v>
+        <v>0.9418</v>
       </c>
       <c r="W3" t="n">
-        <v>0.894</v>
+        <v>1.506</v>
       </c>
       <c r="X3" t="n">
         <v>-0.5642</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. MENDEZ BLANCO</t>
+          <t>P. ROSSI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.861</v>
+        <v>0.8633</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5861</v>
+        <v>1.369</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7251</v>
+        <v>-0.5057</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9314</v>
+        <v>-1.6348</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8791</v>
+        <v>0.1697</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0523</v>
+        <v>-1.8046</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9281</v>
+        <v>0.2638</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3141</v>
+        <v>1.3677</v>
       </c>
       <c r="L4" t="n">
-        <v>0.614</v>
+        <v>-1.1038</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9967</v>
+        <v>-1.8987</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.435</v>
+        <v>-1.1979</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5617</v>
+        <v>-0.7008</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.194</v>
+        <v>-1.1642</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3582</v>
+        <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1763</v>
+        <v>1.3921</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6539</v>
+        <v>1.3753</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5224</v>
+        <v>0.0168</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9418</v>
+        <v>0.3299</v>
       </c>
       <c r="W4" t="n">
-        <v>1.506</v>
+        <v>0.894</v>
       </c>
       <c r="X4" t="n">
         <v>-0.5642</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. BIERSACK LOPEZ</t>
+          <t>S. PARADELA PARIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3945</v>
+        <v>-0.3881</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6236</v>
+        <v>-1.3596</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.2291</v>
+        <v>0.9714</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5052</v>
+        <v>-1.2248</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1598</v>
+        <v>-0.9351</v>
       </c>
       <c r="I5" t="n">
-        <v>1.665</v>
+        <v>-0.2897</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6819</v>
+        <v>-1.5301</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0381</v>
+        <v>-0.9845</v>
       </c>
       <c r="L5" t="n">
-        <v>2.6438</v>
+        <v>-0.5455</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1767</v>
+        <v>0.3052</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1979</v>
+        <v>0.0494</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9788</v>
+        <v>0.2558</v>
       </c>
       <c r="P5" t="n">
+        <v>0.5821</v>
+      </c>
+      <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-1.1642</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6191</v>
+        <v>0.2546</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1058</v>
+        <v>0.1705</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5133</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.7298</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.7298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GARCIA QUILEZ CUERVAS</t>
+          <t>D. MAGANTO LUCAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004</v>
+        <v>-0.4699</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2652</v>
+        <v>0.7472</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.2612</v>
+        <v>-1.2171</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.2368</v>
       </c>
       <c r="H6" t="n">
-        <v>1.071</v>
+        <v>0.1606</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2953</v>
+        <v>0.0762</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4761</v>
+        <v>2.4195</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0216</v>
+        <v>1.5036</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5455</v>
+        <v>0.9159</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2996</v>
+        <v>-2.1827</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0494</v>
+        <v>-1.3429</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2502</v>
+        <v>-0.8398</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9702</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q6" t="n">
+        <v>-2.1344</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.1642</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.8754</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.4621</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.4133</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.6119</v>
+      </c>
+      <c r="W6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
-        <v>0.9702</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.4237</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.4226</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-2.1657</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.788</v>
-      </c>
       <c r="X6" t="n">
-        <v>-3.9537</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. PARADELA PARIS</t>
+          <t>A. GARCIA QUILEZ CUERVAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0671</v>
+        <v>-0.4717</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8205</v>
+        <v>2.2257</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7534</v>
+        <v>-2.6973</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2248</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9351</v>
+        <v>1.071</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2897</v>
+        <v>-0.2953</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5301</v>
+        <v>0.4761</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9845</v>
+        <v>1.0216</v>
       </c>
       <c r="L7" t="n">
         <v>-0.5455</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3052</v>
+        <v>0.2996</v>
       </c>
       <c r="N7" t="n">
         <v>0.0494</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2558</v>
+        <v>0.2502</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5821</v>
+        <v>0.9702</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5821</v>
+        <v>0.9702</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4244</v>
+        <v>-0.0519</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2905</v>
+        <v>-0.0384</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1339</v>
+        <v>-0.0134</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.1657</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.788</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-3.9537</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. MAGANTO LUCAS</t>
+          <t>A. BIERSACK LOPEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0981</v>
+        <v>-0.476</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2353</v>
+        <v>2.9439</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8628</v>
+        <v>-3.4199</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2368</v>
+        <v>1.5052</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1606</v>
+        <v>-0.1598</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0762</v>
+        <v>1.665</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4195</v>
+        <v>3.6819</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5036</v>
+        <v>1.0381</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9159</v>
+        <v>2.6438</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1827</v>
+        <v>-2.1767</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3429</v>
+        <v>-1.1979</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8398</v>
+        <v>-0.9788</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1344</v>
+        <v>-1.1642</v>
       </c>
       <c r="R8" t="n">
         <v>1.1642</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2472</v>
+        <v>0.7487</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5204</v>
+        <v>0.4262</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.3225</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6119</v>
+        <v>-2.7298</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6119</v>
+        <v>-2.7298</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4101</v>
+        <v>-0.6493</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6464</v>
+        <v>3.1074</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.0564</v>
+        <v>-3.7566</v>
       </c>
       <c r="G9" t="n">
         <v>2.9475</v>
@@ -1156,13 +1156,13 @@
         <v>1.5523</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3277</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4599</v>
+        <v>0.0011</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8679</v>
+        <v>-0.5681</v>
       </c>
       <c r="V9" t="n">
         <v>-2.4477</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4487</v>
+        <v>-1.6067</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7881</v>
+        <v>-3.0279</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3394</v>
+        <v>1.4211</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9505</v>
@@ -1234,13 +1234,13 @@
         <v>0.7761</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0063</v>
+        <v>-0.1517</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4251</v>
+        <v>0.1853</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4188</v>
+        <v>-0.337</v>
       </c>
       <c r="V10" t="n">
         <v>0.6597</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7744</v>
+        <v>-2.2439</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7317</v>
+        <v>-0.3103</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0426</v>
+        <v>-1.9336</v>
       </c>
       <c r="G11" t="n">
         <v>1.435</v>
@@ -1312,13 +1312,13 @@
         <v>1.1642</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7034</v>
+        <v>-0.173</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2053</v>
+        <v>0.2162</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4982</v>
+        <v>-0.3892</v>
       </c>
       <c r="V11" t="n">
         <v>-2.7298</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.7402</v>
+        <v>7.648699999999998</v>
       </c>
       <c r="E12" t="n">
-        <v>16.7814</v>
+        <v>17.6898</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.041</v>
+        <v>-10.0411</v>
       </c>
       <c r="G12" t="n">
         <v>10.2389</v>
@@ -1375,13 +1375,13 @@
         <v>-8.6625</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.075100000000001</v>
+        <v>-5.0751</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.5873</v>
+        <v>-3.587299999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Q12" t="n">
         <v>-12.6121</v>
@@ -1390,16 +1390,16 @@
         <v>12.6121</v>
       </c>
       <c r="S12" t="n">
-        <v>2.243200000000001</v>
+        <v>3.1516</v>
       </c>
       <c r="T12" t="n">
-        <v>2.6803</v>
+        <v>3.5889</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4373</v>
+        <v>-0.4373000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.741600000000001</v>
+        <v>-5.7416</v>
       </c>
       <c r="W12" t="n">
         <v>7.8118</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. NIANG</t>
+          <t>A. APARICIO IZQUIERDO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.3547</v>
+        <v>2.5824</v>
       </c>
       <c r="E13" t="n">
-        <v>4.85</v>
+        <v>6.3111</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4953</v>
+        <v>-3.7287</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4312</v>
+        <v>-1.8045</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7382</v>
+        <v>-2.1404</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.307</v>
+        <v>0.3359</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4749</v>
+        <v>1.9586</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6807</v>
+        <v>-0.5684</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7942</v>
+        <v>2.5271</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.0437</v>
+        <v>-3.7631</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9425</v>
+        <v>-1.572</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1011</v>
+        <v>-2.1912</v>
       </c>
       <c r="P13" t="n">
+        <v>1.5523</v>
+      </c>
+      <c r="Q13" t="n">
         <v>-0.194</v>
       </c>
-      <c r="Q13" t="n">
-        <v>-0.9702</v>
-      </c>
       <c r="R13" t="n">
-        <v>0.7761</v>
+        <v>1.7463</v>
       </c>
       <c r="S13" t="n">
-        <v>1.734</v>
+        <v>0.1794</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2752</v>
+        <v>0.263</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4588</v>
+        <v>-0.0835</v>
       </c>
       <c r="V13" t="n">
-        <v>1.3836</v>
+        <v>2.6552</v>
       </c>
       <c r="W13" t="n">
-        <v>2.0701</v>
+        <v>4.2836</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6866</v>
+        <v>-1.6283</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Y. RODRÍGUEZ MACHÍN</t>
+          <t>M. NIANG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9228</v>
+        <v>2.5149</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0667</v>
+        <v>4.1493</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1439</v>
+        <v>-1.6344</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2609</v>
+        <v>0.4312</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2142</v>
+        <v>0.7382</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0467</v>
+        <v>-0.307</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1015</v>
+        <v>2.4749</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3707</v>
+        <v>1.6807</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7307</v>
+        <v>0.7942</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8406</v>
+        <v>-2.0437</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1565</v>
+        <v>-0.9425</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-1.1011</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3881</v>
+        <v>-0.194</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3582</v>
+        <v>0.7761</v>
       </c>
       <c r="S14" t="n">
-        <v>1.05</v>
+        <v>0.8942</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7115</v>
+        <v>0.5745</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6615</v>
+        <v>0.3197</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2239</v>
+        <v>1.3836</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2239</v>
+        <v>2.0701</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.6866</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. APARICIO IZQUIERDO</t>
+          <t>Y. RODRÍGUEZ MACHÍN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5918</v>
+        <v>1.8824</v>
       </c>
       <c r="E15" t="n">
-        <v>6.9117</v>
+        <v>1.8655</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.3199</v>
+        <v>0.0169</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.8045</v>
+        <v>0.2609</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.1404</v>
+        <v>0.2142</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3359</v>
+        <v>0.0467</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9586</v>
+        <v>1.1015</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5684</v>
+        <v>0.3707</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5271</v>
+        <v>0.7307</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.7631</v>
+        <v>-0.8406</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.572</v>
+        <v>-0.1565</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.1912</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5523</v>
+        <v>0.3881</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7463</v>
+        <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1889</v>
+        <v>0.0095</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8636</v>
+        <v>0.5103</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6747</v>
+        <v>-0.5008</v>
       </c>
       <c r="V15" t="n">
-        <v>2.6552</v>
+        <v>1.2239</v>
       </c>
       <c r="W15" t="n">
-        <v>4.2836</v>
+        <v>1.2239</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.6283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8057</v>
+        <v>-1.0726</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0495</v>
+        <v>0.6491</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8552</v>
+        <v>-1.7217</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7116</v>
@@ -1702,13 +1702,13 @@
         <v>1.3582</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3522</v>
+        <v>0.0852</v>
       </c>
       <c r="T16" t="n">
-        <v>0.729</v>
+        <v>0.3286</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3768</v>
+        <v>-0.2434</v>
       </c>
       <c r="V16" t="n">
         <v>0.3299</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. OJEDA DAVILA</t>
+          <t>J. RIES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5648</v>
+        <v>-1.3001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7294</v>
+        <v>-0.8477</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2942</v>
+        <v>-0.4524</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.8115</v>
+        <v>-0.8111</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.29</v>
+        <v>0.1516</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5215</v>
+        <v>-0.9626</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4255</v>
+        <v>0.1136</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4119</v>
+        <v>0.6591</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.8374</v>
+        <v>-0.5455</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.386</v>
+        <v>-0.9246</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7019</v>
+        <v>-0.5075</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.4171</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5523</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q17" t="n">
+        <v>-1.9403</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.9702</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.7428</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.2448</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.498</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.2239</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.2239</v>
+      </c>
+      <c r="X17" t="n">
         <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.5523</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-0.3638</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-0.3511</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-0.0128</v>
-      </c>
-      <c r="V17" t="n">
-        <v>-0.9418</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.506</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-2.4477</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RIES</t>
+          <t>D. OJEDA DAVILA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8429</v>
+        <v>-1.3858</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.148</v>
+        <v>0.8295</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6949</v>
+        <v>-2.2153</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8111</v>
+        <v>-1.8115</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1516</v>
+        <v>-0.29</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9626</v>
+        <v>-1.5215</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1136</v>
+        <v>-0.4255</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6591</v>
+        <v>0.4119</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5455</v>
+        <v>-0.8374</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9246</v>
+        <v>-1.386</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5075</v>
+        <v>-0.7019</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4171</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9702</v>
+        <v>1.5523</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9702</v>
+        <v>1.5523</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2855</v>
+        <v>-0.1848</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5451</v>
+        <v>-0.251</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7403999999999999</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2239</v>
+        <v>-0.9418</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2239</v>
+        <v>1.506</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. GARCÍA PEREZ</t>
+          <t>I. REBERGEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9978</v>
+        <v>-1.4445</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8435</v>
+        <v>1.0902</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1543</v>
+        <v>-2.5347</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0721</v>
+        <v>-0.8198</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6171</v>
+        <v>0.7407</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.545</v>
+        <v>-1.5605</v>
       </c>
       <c r="J19" t="n">
-        <v>0.968</v>
+        <v>2.0645</v>
       </c>
       <c r="K19" t="n">
-        <v>0.968</v>
+        <v>1.9732</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.896</v>
+        <v>-2.8843</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.351</v>
+        <v>-1.2325</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.545</v>
+        <v>-1.6517</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7761</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9702</v>
+        <v>-2.1344</v>
       </c>
       <c r="R19" t="n">
-        <v>0.194</v>
+        <v>1.7463</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3519</v>
+        <v>-0.3485</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1817</v>
+        <v>-0.2981</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1702</v>
+        <v>-0.0504</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9418</v>
+        <v>0.1119</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6597</v>
+        <v>1.4582</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2821</v>
+        <v>-1.3463</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. RODRÍGUEZ RIVEROL</t>
+          <t>E. GARCÍA PEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6452</v>
+        <v>-1.8732</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5984</v>
+        <v>-0.7433999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0468</v>
+        <v>-1.1298</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9638</v>
+        <v>0.0721</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6624</v>
+        <v>0.6171</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3014</v>
+        <v>-0.545</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2504</v>
+        <v>0.968</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1236</v>
+        <v>0.968</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1268</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2142</v>
+        <v>-0.896</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.786</v>
+        <v>-0.351</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4282</v>
+        <v>-0.545</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3582</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1344</v>
+        <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2007</v>
+        <v>-0.2274</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7145</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5137</v>
+        <v>-0.1458</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1224</v>
+        <v>-0.9418</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1224</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. REBERGEN</t>
+          <t>M. RODRÍGUEZ RIVEROL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8548</v>
+        <v>-2.1475</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1893</v>
+        <v>-2.0979</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0441</v>
+        <v>-0.0496</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8198</v>
+        <v>-0.9638</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7407</v>
+        <v>-0.6624</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5605</v>
+        <v>-0.3014</v>
       </c>
       <c r="J21" t="n">
-        <v>2.0645</v>
+        <v>0.2504</v>
       </c>
       <c r="K21" t="n">
-        <v>1.9732</v>
+        <v>0.1236</v>
       </c>
       <c r="L21" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.1268</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.8843</v>
+        <v>-1.2142</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2325</v>
+        <v>-0.786</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.6517</v>
+        <v>-0.4282</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3881</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.1344</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7463</v>
+        <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7588</v>
+        <v>0.2969</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.199</v>
+        <v>-0.214</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5599</v>
+        <v>0.5109</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1119</v>
+        <v>-0.1224</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4582</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.3463</v>
+        <v>-0.1224</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8983</v>
+        <v>-2.4941</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.1655</v>
+        <v>-1.1645</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7328</v>
+        <v>-1.3295</v>
       </c>
       <c r="G22" t="n">
         <v>-4.0806</v>
@@ -2170,13 +2170,13 @@
         <v>2.1344</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6072</v>
+        <v>-0.203</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1508</v>
+        <v>-0.1498</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4564</v>
+        <v>-0.0532</v>
       </c>
       <c r="V22" t="n">
         <v>0.8194</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.740199999999998</v>
+        <v>-4.738100000000001</v>
       </c>
       <c r="E23" t="n">
         <v>10.0412</v>
       </c>
       <c r="F23" t="n">
-        <v>-16.7814</v>
+        <v>-14.7792</v>
       </c>
       <c r="G23" t="n">
         <v>-10.2387</v>
@@ -2248,13 +2248,13 @@
         <v>12.6121</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.2428</v>
+        <v>-0.2413</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4370999999999996</v>
+        <v>0.4371000000000002</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.6802</v>
+        <v>-0.6783000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>5.7418</v>
